--- a/products-storage/07-uderzhaniya-shtrafy-zachety/06-grafik-vozmeshcheniya.xlsx
+++ b/products-storage/07-uderzhaniya-shtrafy-zachety/06-grafik-vozmeshcheniya.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="D4" s="2">
-        <f>СУММ(D2:D10)</f>
+        <f>SUM(D2:D10)</f>
         <v/>
       </c>
       <c r="E4" s="2" t="inlineStr"/>

--- a/products-storage/07-uderzhaniya-shtrafy-zachety/06-grafik-vozmeshcheniya.xlsx
+++ b/products-storage/07-uderzhaniya-shtrafy-zachety/06-grafik-vozmeshcheniya.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="График возмещения удержанных сумм" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="График возмещения" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -536,20 +536,83 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="A4" s="2" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr"/>
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>ИТОГО:</t>
         </is>
       </c>
-      <c r="D4" s="2">
+      <c r="D11" s="2">
         <f>SUM(D2:D10)</f>
         <v/>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
